--- a/data/trans_bre/P2A_fisi_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_fisi_R-Habitat-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 1,85</t>
+          <t>-3,47; 1,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 0,55</t>
+          <t>-5,34; 0,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 0,0</t>
+          <t>-3,2; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 3,66</t>
+          <t>-6,68; 3,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-66,74; 87,43</t>
+          <t>-67,3; 91,09</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,44; -0,36</t>
+          <t>-6,04; -0,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 4,4</t>
+          <t>-2,71; 4,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 3,29</t>
+          <t>-2,56; 2,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 0,25</t>
+          <t>-7,5; 0,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 42,62</t>
+          <t>-100,0; 40,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,93; 225,73</t>
+          <t>-54,76; 241,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-72,7; 371,17</t>
+          <t>-71,81; 304,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-75,7; 7,76</t>
+          <t>-75,11; 5,1</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 3,07</t>
+          <t>-5,47; 3,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,9; -0,41</t>
+          <t>-6,99; -0,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 0,0</t>
+          <t>-5,52; 0,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 4,75</t>
+          <t>-9,87; 4,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-82,15; 186,34</t>
+          <t>-80,7; 260,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 39,24</t>
+          <t>-100,0; 30,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-70,92; 134,98</t>
+          <t>-74,12; 109,97</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 1,65</t>
+          <t>-4,31; 1,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 4,31</t>
+          <t>-3,55; 4,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 7,18</t>
+          <t>-0,6; 7,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 5,49</t>
+          <t>-1,54; 5,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-88,04; 124,98</t>
+          <t>-86,08; 122,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,61; 233,09</t>
+          <t>-71,01; 232,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,54; 508,77</t>
+          <t>-26,92; 559,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,21; 444,0</t>
+          <t>-36,35; 380,04</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,26; -0,1</t>
+          <t>-3,54; -0,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,04</t>
+          <t>-2,61; 1,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 2,18</t>
+          <t>-1,2; 1,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 1,41</t>
+          <t>-3,54; 1,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-74,84; -0,71</t>
+          <t>-74,73; -7,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-56,6; 38,77</t>
+          <t>-57,32; 43,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-41,46; 138,67</t>
+          <t>-44,88; 137,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-43,62; 28,75</t>
+          <t>-45,97; 26,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_fisi_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_fisi_R-Habitat-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 1,9</t>
+          <t>-3,57; 1,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 0,56</t>
+          <t>-5,11; 0,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 0,0</t>
+          <t>-3,5; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 3,29</t>
+          <t>-6,6; 3,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-67,3; 91,09</t>
+          <t>-67,06; 114,46</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,04; -0,43</t>
+          <t>-6,49; -0,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 4,8</t>
+          <t>-2,57; 4,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 2,99</t>
+          <t>-2,56; 3,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 0,18</t>
+          <t>-7,41; 0,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 40,79</t>
+          <t>-100,0; 19,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,76; 241,68</t>
+          <t>-53,62; 258,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-71,81; 304,89</t>
+          <t>-74,07; 441,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-75,11; 5,1</t>
+          <t>-75,96; 8,93</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 3,02</t>
+          <t>-5,51; 2,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,99; -0,55</t>
+          <t>-6,95; -0,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 0,22</t>
+          <t>-5,66; -0,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 4,16</t>
+          <t>-7,47; 4,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-80,7; 260,55</t>
+          <t>-87,17; 127,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 30,95</t>
+          <t>-100,0; 41,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-74,12; 109,97</t>
+          <t>-69,14; 150,93</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 1,67</t>
+          <t>-4,78; 1,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 4,02</t>
+          <t>-3,34; 4,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 7,38</t>
+          <t>-0,62; 6,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 5,6</t>
+          <t>-1,43; 5,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-86,08; 122,9</t>
+          <t>-87,7; 117,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,01; 232,05</t>
+          <t>-68,53; 283,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,92; 559,59</t>
+          <t>-30,79; 520,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,35; 380,04</t>
+          <t>-36,71; 422,89</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,54; -0,31</t>
+          <t>-3,44; -0,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 1,08</t>
+          <t>-2,45; 1,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,97</t>
+          <t>-1,13; 1,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 1,22</t>
+          <t>-3,53; 1,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-74,73; -7,79</t>
+          <t>-74,46; -2,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-57,32; 43,35</t>
+          <t>-55,34; 42,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-44,88; 137,13</t>
+          <t>-38,88; 127,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-45,97; 26,83</t>
+          <t>-46,3; 25,01</t>
         </is>
       </c>
     </row>
